--- a/data_lake/industry/TrendForce/TFT LCD.xlsx
+++ b/data_lake/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A35781-1A48-4EF8-9799-D1764D7DF65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953FC4C0-C9CA-45F1-BCE7-70D18523B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -174,24 +174,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -204,7 +204,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -229,26 +229,29 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -270,7 +273,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -283,81 +286,81 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -636,18 +639,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.1796875" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="25" width="9" style="15"/>
+    <col min="1" max="1" width="9.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.796875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="9.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="9" style="15"/>
     <col min="26" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="9" customFormat="1">
+    <row r="1" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -706,7 +710,7 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="8"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
@@ -757,7 +761,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>46042</v>
       </c>
@@ -816,7 +820,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>46077</v>
       </c>
@@ -875,7 +879,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>46104</v>
       </c>
@@ -925,7 +929,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>46132</v>
       </c>
@@ -975,7 +979,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>46162</v>
       </c>
@@ -1025,7 +1029,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>46195</v>
       </c>
@@ -1090,22 +1094,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Y9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.7265625" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.54296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.69921875" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.5" style="28" bestFit="1" customWidth="1"/>
     <col min="13" max="25" width="9" style="29"/>
-    <col min="26" max="16384" width="9" style="23"/>
+    <col min="26" max="16384" width="9" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="21" customFormat="1">
+    <row r="1" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -1142,21 +1146,21 @@
       <c r="L1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>
@@ -1185,31 +1189,31 @@
       <c r="L2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="27">
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="25">
         <v>46022</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="25">
         <v>46022</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="19">
@@ -1236,31 +1240,31 @@
       <c r="L3" s="19">
         <v>6.9</v>
       </c>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="27">
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="25">
         <v>46052</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <v>46052</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="19">
@@ -1287,31 +1291,31 @@
       <c r="L4" s="19">
         <v>6.8</v>
       </c>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="27">
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="25">
         <v>46079</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="25">
         <v>46079</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="28">
@@ -1339,17 +1343,17 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="27">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
         <v>46111</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <v>46111</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="28">
@@ -1377,17 +1381,17 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="27">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="25">
         <v>46141</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="25">
         <v>46141</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="28">
@@ -1415,17 +1419,17 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="27">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
         <v>46171</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="25">
         <v>46171</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="28">
@@ -1451,6 +1455,44 @@
       </c>
       <c r="L8" s="28">
         <v>6.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="25">
+        <v>46203</v>
+      </c>
+      <c r="B9" s="25">
+        <v>46203</v>
+      </c>
+      <c r="C9" s="26">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="28">
+        <v>1.2</v>
+      </c>
+      <c r="F9" s="28">
+        <v>1.7</v>
+      </c>
+      <c r="G9" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="H9" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="I9" s="28">
+        <v>5.7</v>
+      </c>
+      <c r="J9" s="28">
+        <v>8.5</v>
+      </c>
+      <c r="K9" s="28">
+        <v>6.2</v>
+      </c>
+      <c r="L9" s="28">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1467,19 +1509,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
-  <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.90625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.8984375" style="28" customWidth="1"/>
     <col min="25" max="25" width="9" style="29"/>
-    <col min="26" max="16384" width="9" style="23"/>
+    <col min="26" max="16384" width="9" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="21" customFormat="1">
+    <row r="1" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -1552,9 +1594,9 @@
       <c r="X1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="20"/>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>
@@ -1619,19 +1661,19 @@
       <c r="X2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="22"/>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="24">
+      <c r="Y2" s="23"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="30">
         <v>45991</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="30">
         <v>45991</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="19">
@@ -1668,19 +1710,19 @@
         <v>160.4</v>
       </c>
       <c r="X3" s="19"/>
-      <c r="Y3" s="22"/>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="27">
+      <c r="Y3" s="23"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="25">
         <v>46022</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <v>46022</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="19">
@@ -1743,19 +1785,19 @@
       <c r="X4" s="19">
         <v>160.4</v>
       </c>
-      <c r="Y4" s="22"/>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="27">
+      <c r="Y4" s="23"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="25">
         <v>46052</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="25">
         <v>46052</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="19">
@@ -1818,19 +1860,19 @@
       <c r="X5" s="19">
         <v>160.9</v>
       </c>
-      <c r="Y5" s="22"/>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="27">
+      <c r="Y5" s="23"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
         <v>46079</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <v>46079</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="28">
@@ -1894,17 +1936,17 @@
         <v>161.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="27">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="25">
         <v>46119</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="25">
         <v>46119</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="28">
@@ -1968,17 +2010,17 @@
         <v>161.80000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="27">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
         <v>46141</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="25">
         <v>46141</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="28">
@@ -2042,17 +2084,17 @@
         <v>169.8</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="27">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="25">
         <v>46171</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="25">
         <v>46171</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="28">
@@ -2114,6 +2156,80 @@
       </c>
       <c r="X9" s="28">
         <v>168.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="25">
+        <v>46203</v>
+      </c>
+      <c r="B10" s="25">
+        <v>46203</v>
+      </c>
+      <c r="C10" s="26">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="28">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="F10" s="28">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="G10" s="28">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="H10" s="28">
+        <v>75.5</v>
+      </c>
+      <c r="I10" s="28">
+        <v>100.1</v>
+      </c>
+      <c r="J10" s="28">
+        <v>140</v>
+      </c>
+      <c r="K10" s="28">
+        <v>101.1</v>
+      </c>
+      <c r="L10" s="28">
+        <v>100.7</v>
+      </c>
+      <c r="M10" s="28">
+        <v>229</v>
+      </c>
+      <c r="N10" s="28">
+        <v>333.3</v>
+      </c>
+      <c r="O10" s="28">
+        <v>292.3</v>
+      </c>
+      <c r="P10" s="28">
+        <v>302.8</v>
+      </c>
+      <c r="Q10" s="28">
+        <v>382.4</v>
+      </c>
+      <c r="R10" s="28">
+        <v>452.2</v>
+      </c>
+      <c r="S10" s="28">
+        <v>417.5</v>
+      </c>
+      <c r="T10" s="28">
+        <v>413.6</v>
+      </c>
+      <c r="U10" s="28">
+        <v>156.5</v>
+      </c>
+      <c r="V10" s="28">
+        <v>219.8</v>
+      </c>
+      <c r="W10" s="28">
+        <v>172.9</v>
+      </c>
+      <c r="X10" s="28">
+        <v>168.5</v>
       </c>
     </row>
   </sheetData>
@@ -2132,24 +2248,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="29"/>
-    <col min="26" max="16384" width="9" style="23"/>
+    <col min="26" max="16384" width="9" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="21" customFormat="1">
+    <row r="1" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -2192,19 +2308,19 @@
       <c r="N1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="20"/>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>
@@ -2239,26 +2355,26 @@
       <c r="N2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="27">
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="25">
         <v>45962</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="31">
@@ -2291,29 +2407,29 @@
       <c r="N3" s="31">
         <v>19987</v>
       </c>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="27">
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="25">
         <v>45992</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <v>46042</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="31">
@@ -2346,29 +2462,29 @@
       <c r="N4" s="31">
         <v>21591</v>
       </c>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="27">
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="25">
         <v>46023</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="25">
         <v>46079</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="32">
@@ -2402,17 +2518,17 @@
         <v>21064</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="27">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
         <v>46054</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <v>46106</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="32">
@@ -2446,17 +2562,17 @@
         <v>18066</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="27">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="25">
         <v>46082</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="25">
         <v>46133</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="32">
@@ -2490,17 +2606,17 @@
         <v>22289</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="27">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
         <v>46113</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="25">
         <v>46162</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="32">
@@ -2534,17 +2650,17 @@
         <v>20053</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="27">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="25">
         <v>46143</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="25">
         <v>46196</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="27" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="32">
@@ -2593,20 +2709,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.3984375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2614,19 +2730,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2634,13 +2750,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2648,31 +2764,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -2680,25 +2796,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>18</v>

--- a/data_lake/industry/TrendForce/TFT LCD.xlsx
+++ b/data_lake/industry/TrendForce/TFT LCD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953FC4C0-C9CA-45F1-BCE7-70D18523B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E432B77D-1B07-4060-BBB4-5FC84BD729E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,19 +229,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -277,7 +264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -286,14 +273,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -315,48 +296,24 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -639,443 +596,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="9.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="25" width="9" style="15"/>
-    <col min="26" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="9.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="9" style="14"/>
+    <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="10" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>46042</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>46042</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="11">
         <v>0.5</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <v>115</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="8">
         <v>125</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>122</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>121</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="8">
         <v>57.6</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>65.8</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="8">
         <v>63</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="8">
         <v>63</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="8">
         <v>26.3</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="8">
         <v>28</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="8">
         <v>26.8</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="8">
         <v>26.9</v>
       </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>46077</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>46077</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <v>0.5</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>117</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="8">
         <v>127</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>124</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>122</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>57.6</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="8">
         <v>65.8</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <v>63</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="8">
         <v>63</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="8">
         <v>26.2</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="8">
         <v>27.9</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="8">
         <v>26.7</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="8">
         <v>26.8</v>
       </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>46104</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>46104</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="11">
         <v>0.5</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <v>119</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>129</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="14">
         <v>126</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="14">
         <v>124</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="14">
         <v>57.7</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="14">
         <v>66</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14">
         <v>63.1</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="14">
         <v>63</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="14">
         <v>26.2</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="14">
         <v>27.9</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="14">
         <v>26.7</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="14">
         <v>26.7</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>46132</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>46132</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>0.5</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <v>119</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <v>129</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>126</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>126</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <v>57.8</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <v>66.2</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <v>63.3</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="14">
         <v>63.1</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="14">
         <v>26.2</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <v>27.9</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <v>26.7</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="14">
         <v>26.7</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>46162</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>46162</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>0.5</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <v>119</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>129</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <v>126</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <v>126</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="14">
         <v>57.9</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <v>66.400000000000006</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="14">
         <v>63.5</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="14">
         <v>63.3</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="14">
         <v>26.2</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="14">
         <v>27.9</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="14">
         <v>26.7</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="14">
         <v>26.7</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>46195</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>46195</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>119</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>129</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <v>126</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>126</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="14">
         <v>58</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="14">
         <v>66.400000000000006</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="14">
         <v>63.6</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="14">
         <v>63.5</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="14">
         <v>26.2</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="14">
         <v>27.9</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="14">
         <v>26.7</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="14">
         <v>26.7</v>
       </c>
     </row>
@@ -1097,401 +1054,401 @@
   <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.69921875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="25" width="9" style="29"/>
-    <col min="26" max="16384" width="9" style="24"/>
+    <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.69921875" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="9" style="14"/>
+    <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+      <c r="A3" s="10">
         <v>46022</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="10">
         <v>46022</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="4">
         <v>1.2</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="4">
         <v>1.7</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="4">
         <v>1.4</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="4">
         <v>1.4</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="4">
         <v>5.7</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="4">
         <v>8.5</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="4">
         <v>6.8</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="4">
         <v>6.9</v>
       </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="10">
         <v>46052</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="10">
         <v>46052</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="4">
         <v>1.2</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="4">
         <v>1.7</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="4">
         <v>1.4</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="4">
         <v>1.4</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="4">
         <v>5.7</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="4">
         <v>8.5</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="4">
         <v>6.7</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="4">
         <v>6.8</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="10">
         <v>46079</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="10">
         <v>46079</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="13">
         <v>1.2</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="13">
         <v>1.7</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="13">
         <v>1.4</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="13">
         <v>1.4</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="13">
         <v>5.7</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="13">
         <v>8.5</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="13">
         <v>6.6</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="13">
         <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="10">
         <v>46111</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="10">
         <v>46111</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="13">
         <v>1.2</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="13">
         <v>1.7</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="13">
         <v>1.4</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="13">
         <v>1.4</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="13">
         <v>5.7</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="13">
         <v>8.5</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="13">
         <v>6.5</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="13">
         <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="10">
         <v>46141</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="10">
         <v>46141</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="13">
         <v>1.2</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="13">
         <v>1.7</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="13">
         <v>1.4</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="13">
         <v>1.4</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="13">
         <v>5.7</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="13">
         <v>8.5</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="13">
         <v>6.4</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="13">
         <v>6.5</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="10">
         <v>46171</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="10">
         <v>46171</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="13">
         <v>1.2</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="13">
         <v>1.7</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="13">
         <v>1.4</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="13">
         <v>1.4</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="13">
         <v>5.7</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="13">
         <v>8.5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="13">
         <v>6.3</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="13">
         <v>6.4</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="A9" s="10">
         <v>46203</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="10">
         <v>46203</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="13">
         <v>1.2</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="13">
         <v>1.7</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="13">
         <v>1.4</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="13">
         <v>1.4</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="13">
         <v>5.7</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="13">
         <v>8.5</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="13">
         <v>6.2</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="13">
         <v>6.3</v>
       </c>
     </row>
@@ -1512,723 +1469,723 @@
   <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.8984375" style="28" customWidth="1"/>
-    <col min="25" max="25" width="9" style="29"/>
-    <col min="26" max="16384" width="9" style="24"/>
+    <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.8984375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="9" style="14"/>
+    <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="19" t="s">
+      <c r="W1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="X1" s="19" t="s">
+      <c r="X1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="21"/>
+      <c r="Y1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="R2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="S2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="T2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="V2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="W2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="19" t="s">
+      <c r="X2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="23"/>
+      <c r="Y2" s="8"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="30">
+      <c r="A3" s="15">
         <v>45991</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="15">
         <v>45991</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="4">
         <v>72</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="4">
         <v>72</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="4">
         <v>72</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
         <v>94</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4">
         <v>297.5</v>
       </c>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4">
         <v>395.3</v>
       </c>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="19">
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4">
         <v>160.4</v>
       </c>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="23"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="10">
         <v>46022</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="10">
         <v>46022</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="4">
         <v>72.8</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="4">
         <v>72.8</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="4">
         <v>72.8</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="4">
         <v>72</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="4">
         <v>91.4</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="4">
         <v>130</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="4">
         <v>94.4</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="4">
         <v>94</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="4">
         <v>246.7</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="4">
         <v>305.8</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="4">
         <v>293.7</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="4">
         <v>297.5</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="4">
         <v>362.2</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="4">
         <v>410.1</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="4">
         <v>387.3</v>
       </c>
-      <c r="T4" s="19">
+      <c r="T4" s="4">
         <v>395.3</v>
       </c>
-      <c r="U4" s="19">
+      <c r="U4" s="4">
         <v>149.19999999999999</v>
       </c>
-      <c r="V4" s="19">
+      <c r="V4" s="4">
         <v>195.1</v>
       </c>
-      <c r="W4" s="19">
+      <c r="W4" s="4">
         <v>160.9</v>
       </c>
-      <c r="X4" s="19">
+      <c r="X4" s="4">
         <v>160.4</v>
       </c>
-      <c r="Y4" s="23"/>
+      <c r="Y4" s="8"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="10">
         <v>46052</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="10">
         <v>46052</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="4">
         <v>73.599999999999994</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="4">
         <v>73.599999999999994</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="4">
         <v>73.599999999999994</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="4">
         <v>72.8</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="4">
         <v>94.9</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="4">
         <v>142.30000000000001</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="4">
         <v>96.9</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="4">
         <v>64.400000000000006</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="4">
         <v>210</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="4">
         <v>309.3</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="4">
         <v>283.3</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="4">
         <v>293.7</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="4">
         <v>375</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="4">
         <v>413.8</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="4">
         <v>391.2</v>
       </c>
-      <c r="T5" s="19">
+      <c r="T5" s="4">
         <v>387.3</v>
       </c>
-      <c r="U5" s="19">
+      <c r="U5" s="4">
         <v>149.80000000000001</v>
       </c>
-      <c r="V5" s="19">
+      <c r="V5" s="4">
         <v>193.2</v>
       </c>
-      <c r="W5" s="19">
+      <c r="W5" s="4">
         <v>161.9</v>
       </c>
-      <c r="X5" s="19">
+      <c r="X5" s="4">
         <v>160.9</v>
       </c>
-      <c r="Y5" s="23"/>
+      <c r="Y5" s="8"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="10">
         <v>46079</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="10">
         <v>46079</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="13">
         <v>74.2</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="13">
         <v>74.2</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="13">
         <v>74.2</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="13">
         <v>73.599999999999994</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="13">
         <v>97.3</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="13">
         <v>144.80000000000001</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="13">
         <v>99.4</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="13">
         <v>96.9</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="13">
         <v>199.4</v>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="13">
         <v>326</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="13">
         <v>298.10000000000002</v>
       </c>
-      <c r="P6" s="28">
+      <c r="P6" s="13">
         <v>283.3</v>
       </c>
-      <c r="Q6" s="28">
+      <c r="Q6" s="13">
         <v>376.4</v>
       </c>
-      <c r="R6" s="28">
+      <c r="R6" s="13">
         <v>418.4</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="13">
         <v>406.3</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="13">
         <v>391.2</v>
       </c>
-      <c r="U6" s="28">
+      <c r="U6" s="13">
         <v>152</v>
       </c>
-      <c r="V6" s="28">
+      <c r="V6" s="13">
         <v>199.1</v>
       </c>
-      <c r="W6" s="28">
+      <c r="W6" s="13">
         <v>161.80000000000001</v>
       </c>
-      <c r="X6" s="28">
+      <c r="X6" s="13">
         <v>161.9</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="10">
         <v>46119</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="10">
         <v>46119</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="13">
         <v>74.599999999999994</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="13">
         <v>74.599999999999994</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="13">
         <v>74.599999999999994</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="13">
         <v>74.2</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="13">
         <v>97.9</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="13">
         <v>158.5</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="13">
         <v>102.8</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="13">
         <v>99.4</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="13">
         <v>210</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="13">
         <v>327.5</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="13">
         <v>302.39999999999998</v>
       </c>
-      <c r="P7" s="28">
+      <c r="P7" s="13">
         <v>298.10000000000002</v>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="13">
         <v>366.5</v>
       </c>
-      <c r="R7" s="28">
+      <c r="R7" s="13">
         <v>423.6</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="13">
         <v>407</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="13">
         <v>406.3</v>
       </c>
-      <c r="U7" s="28">
+      <c r="U7" s="13">
         <v>153.6</v>
       </c>
-      <c r="V7" s="28">
+      <c r="V7" s="13">
         <v>211</v>
       </c>
-      <c r="W7" s="28">
+      <c r="W7" s="13">
         <v>169.8</v>
       </c>
-      <c r="X7" s="28">
+      <c r="X7" s="13">
         <v>161.80000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="10">
         <v>46141</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="10">
         <v>46141</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="13">
         <v>75.099999999999994</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="13">
         <v>75.099999999999994</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="13">
         <v>75.099999999999994</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="13">
         <v>74.599999999999994</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="13">
         <v>98.4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="13">
         <v>150</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="13">
         <v>100.6</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="13">
         <v>102.8</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="13">
         <v>225</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="13">
         <v>341.3</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="13">
         <v>317.39999999999998</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="13">
         <v>302.39999999999998</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="13">
         <v>373.1</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="13">
         <v>428.6</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="13">
         <v>408.9</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="13">
         <v>407</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="13">
         <v>152.9</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="13">
         <v>208</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="13">
         <v>168.7</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="13">
         <v>169.8</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="A9" s="10">
         <v>46171</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="10">
         <v>46171</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="13">
         <v>75.5</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="13">
         <v>75.5</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="13">
         <v>75.5</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="13">
         <v>75.099999999999994</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="13">
         <v>98.9</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="13">
         <v>142.6</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="13">
         <v>100.7</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="13">
         <v>100.6</v>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="13">
         <v>201.1</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="13">
         <v>331.4</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="13">
         <v>302.8</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="13">
         <v>317.39999999999998</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="13">
         <v>386.9</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="13">
         <v>437.7</v>
       </c>
-      <c r="S9" s="28">
+      <c r="S9" s="13">
         <v>413.6</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="13">
         <v>408.9</v>
       </c>
-      <c r="U9" s="28">
+      <c r="U9" s="13">
         <v>152.5</v>
       </c>
-      <c r="V9" s="28">
+      <c r="V9" s="13">
         <v>219.5</v>
       </c>
-      <c r="W9" s="28">
+      <c r="W9" s="13">
         <v>168.5</v>
       </c>
-      <c r="X9" s="28">
+      <c r="X9" s="13">
         <v>168.7</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+      <c r="A10" s="10">
         <v>46203</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="10">
         <v>46203</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="11">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="13">
         <v>75.900000000000006</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="13">
         <v>75.900000000000006</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="13">
         <v>75.900000000000006</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="13">
         <v>75.5</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="13">
         <v>100.1</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="13">
         <v>140</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="13">
         <v>101.1</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="13">
         <v>100.7</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="13">
         <v>229</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="13">
         <v>333.3</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="13">
         <v>292.3</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="13">
         <v>302.8</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="13">
         <v>382.4</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="13">
         <v>452.2</v>
       </c>
-      <c r="S10" s="28">
+      <c r="S10" s="13">
         <v>417.5</v>
       </c>
-      <c r="T10" s="28">
+      <c r="T10" s="13">
         <v>413.6</v>
       </c>
-      <c r="U10" s="28">
+      <c r="U10" s="13">
         <v>156.5</v>
       </c>
-      <c r="V10" s="28">
+      <c r="V10" s="13">
         <v>219.8</v>
       </c>
-      <c r="W10" s="28">
+      <c r="W10" s="13">
         <v>172.9</v>
       </c>
-      <c r="X10" s="28">
+      <c r="X10" s="13">
         <v>168.5</v>
       </c>
     </row>
@@ -2250,447 +2207,447 @@
   <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.59765625" style="32" bestFit="1" customWidth="1"/>
-    <col min="15" max="25" width="9" style="29"/>
-    <col min="26" max="16384" width="9" style="24"/>
+    <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="9" style="14"/>
+    <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="31" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="L2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="31" t="s">
+      <c r="M2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="31" t="s">
+      <c r="N2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+      <c r="A3" s="10">
         <v>45962</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="16">
         <v>24118</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="16">
         <v>738</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="16">
         <v>18186</v>
       </c>
-      <c r="H3" s="31">
+      <c r="H3" s="16">
         <v>1184</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="16">
         <v>13817</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="16">
         <v>2638</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="16">
         <v>20226</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="16">
         <v>15428</v>
       </c>
-      <c r="M3" s="31">
+      <c r="M3" s="16">
         <v>76347</v>
       </c>
-      <c r="N3" s="31">
+      <c r="N3" s="16">
         <v>19987</v>
       </c>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="10">
         <v>45992</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="10">
         <v>46042</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="16">
         <v>26154</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="16">
         <v>786</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="16">
         <v>20229</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="16">
         <v>1306</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="16">
         <v>14924</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="16">
         <v>2849</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="16">
         <v>21536</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="16">
         <v>16649</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="16">
         <v>82844</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="16">
         <v>21591</v>
       </c>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="10">
         <v>46023</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="10">
         <v>46079</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="17">
         <v>21091</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="17">
         <v>591</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="17">
         <v>17998</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="17">
         <v>1163</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="17">
         <v>14139</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="17">
         <v>2690</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="17">
         <v>22008</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5" s="17">
         <v>16619</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="17">
         <v>75236</v>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="17">
         <v>21064</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="10">
         <v>46054</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="10">
         <v>46106</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="17">
         <v>19143</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="17">
         <v>552</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="17">
         <v>14885</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="17">
         <v>950</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="17">
         <v>12274</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="17">
         <v>2362</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="17">
         <v>18459</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="17">
         <v>14203</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="17">
         <v>64762</v>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="17">
         <v>18066</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="10">
         <v>46082</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="10">
         <v>46133</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="17">
         <v>28900</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="17">
         <v>869</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="17">
         <v>22860</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="17">
         <v>1486</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="17">
         <v>15216</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="17">
         <v>2934</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="17">
         <v>21474</v>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="17">
         <v>17001</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="17">
         <v>88450</v>
       </c>
-      <c r="N7" s="32">
+      <c r="N7" s="17">
         <v>22289</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="10">
         <v>46113</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="10">
         <v>46162</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="17">
         <v>21757</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="17">
         <v>640</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="17">
         <v>17526</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="17">
         <v>1137</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="17">
         <v>13612</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="17">
         <v>2650</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="17">
         <v>19931</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="17">
         <v>15627</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="17">
         <v>72827</v>
       </c>
-      <c r="N8" s="32">
+      <c r="N8" s="17">
         <v>20053</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="A9" s="10">
         <v>46143</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="10">
         <v>46196</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="17">
         <v>23916</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="17">
         <v>720</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="17">
         <v>19700</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="17">
         <v>1286</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="17">
         <v>13895</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="17">
         <v>2703</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="17">
         <v>20003</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="17">
         <v>15457</v>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="17">
         <v>77515</v>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="17">
         <v>20165</v>
       </c>
     </row>

--- a/data_lake/industry/TrendForce/TFT LCD.xlsx
+++ b/data_lake/industry/TrendForce/TFT LCD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E432B77D-1B07-4060-BBB4-5FC84BD729E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA0A700-33C3-406A-B881-477953160A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -167,6 +167,9 @@
   <si>
     <t>Worldwide (Area)</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTC+8</t>
   </si>
 </sst>
 </file>
@@ -595,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
@@ -994,10 +997,10 @@
         <v>46195</v>
       </c>
       <c r="C8" s="11">
-        <v>0.75694444444444453</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E8" s="14">
         <v>119</v>
@@ -1033,6 +1036,56 @@
         <v>26.7</v>
       </c>
       <c r="P8" s="14">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>46223</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46223</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="14">
+        <v>117</v>
+      </c>
+      <c r="F9" s="14">
+        <v>127</v>
+      </c>
+      <c r="G9" s="14">
+        <v>124</v>
+      </c>
+      <c r="H9" s="14">
+        <v>126</v>
+      </c>
+      <c r="I9" s="14">
+        <v>58</v>
+      </c>
+      <c r="J9" s="14">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="K9" s="14">
+        <v>63.6</v>
+      </c>
+      <c r="L9" s="14">
+        <v>63.6</v>
+      </c>
+      <c r="M9" s="14">
+        <v>26.2</v>
+      </c>
+      <c r="N9" s="14">
+        <v>27.9</v>
+      </c>
+      <c r="O9" s="14">
+        <v>26.7</v>
+      </c>
+      <c r="P9" s="14">
         <v>26.7</v>
       </c>
     </row>
@@ -2204,7 +2257,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -2649,6 +2702,50 @@
       </c>
       <c r="N9" s="17">
         <v>20165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>46174</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="17">
+        <v>28391</v>
+      </c>
+      <c r="F10" s="17">
+        <v>842</v>
+      </c>
+      <c r="G10" s="17">
+        <v>23561</v>
+      </c>
+      <c r="H10" s="17">
+        <v>1533</v>
+      </c>
+      <c r="I10" s="17">
+        <v>13578</v>
+      </c>
+      <c r="J10" s="17">
+        <v>2650</v>
+      </c>
+      <c r="K10" s="17">
+        <v>19676</v>
+      </c>
+      <c r="L10" s="17">
+        <v>15408</v>
+      </c>
+      <c r="M10" s="17">
+        <v>85206</v>
+      </c>
+      <c r="N10" s="17">
+        <v>20433</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/TFT LCD.xlsx
+++ b/data_lake/industry/TrendForce/TFT LCD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA0A700-33C3-406A-B881-477953160A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B7E4BA-822F-4D59-A8FB-EDF5E8607E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="37">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -1104,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -1505,6 +1505,44 @@
         <v>6.3</v>
       </c>
     </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>46234</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="G10" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H10" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="I10" s="13">
+        <v>5.7</v>
+      </c>
+      <c r="J10" s="13">
+        <v>8.5</v>
+      </c>
+      <c r="K10" s="13">
+        <v>6.2</v>
+      </c>
+      <c r="L10" s="13">
+        <v>6.2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -1519,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -2240,6 +2278,80 @@
       </c>
       <c r="X10" s="13">
         <v>168.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>46234</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="13">
+        <v>75.7</v>
+      </c>
+      <c r="F11" s="13">
+        <v>75.7</v>
+      </c>
+      <c r="G11" s="13">
+        <v>75.7</v>
+      </c>
+      <c r="H11" s="13">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="I11" s="13">
+        <v>99.3</v>
+      </c>
+      <c r="J11" s="13">
+        <v>138.4</v>
+      </c>
+      <c r="K11" s="13">
+        <v>100.2</v>
+      </c>
+      <c r="L11" s="13">
+        <v>101.1</v>
+      </c>
+      <c r="M11" s="13">
+        <v>229</v>
+      </c>
+      <c r="N11" s="13">
+        <v>332.5</v>
+      </c>
+      <c r="O11" s="13">
+        <v>292.7</v>
+      </c>
+      <c r="P11" s="13">
+        <v>292.3</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>387.6</v>
+      </c>
+      <c r="R11" s="13">
+        <v>449.8</v>
+      </c>
+      <c r="S11" s="13">
+        <v>416.5</v>
+      </c>
+      <c r="T11" s="13">
+        <v>417.5</v>
+      </c>
+      <c r="U11" s="13">
+        <v>153.6</v>
+      </c>
+      <c r="V11" s="13">
+        <v>222.4</v>
+      </c>
+      <c r="W11" s="13">
+        <v>172.5</v>
+      </c>
+      <c r="X11" s="13">
+        <v>172.9</v>
       </c>
     </row>
   </sheetData>
@@ -2381,6 +2493,9 @@
       <c r="A3" s="10">
         <v>45962</v>
       </c>
+      <c r="B3" s="10">
+        <v>46014</v>
+      </c>
       <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>

--- a/data_lake/industry/TrendForce/TFT LCD.xlsx
+++ b/data_lake/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B7E4BA-822F-4D59-A8FB-EDF5E8607E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79E6C3B-815D-2748-A324-DCC344A61DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="37">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -177,24 +177,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -207,7 +207,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -263,7 +263,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -276,42 +276,42 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -319,8 +319,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -598,20 +598,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
-  <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.3984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="9.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="9.1640625" style="14" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="14"/>
     <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="7" customFormat="1">
       <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
@@ -670,7 +670,7 @@
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="19"/>
@@ -721,7 +721,7 @@
       <c r="X2" s="8"/>
       <c r="Y2" s="8"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="10">
         <v>46042</v>
       </c>
@@ -780,7 +780,7 @@
       <c r="X3" s="8"/>
       <c r="Y3" s="8"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="10">
         <v>46077</v>
       </c>
@@ -839,7 +839,7 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="10">
         <v>46104</v>
       </c>
@@ -889,7 +889,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="10">
         <v>46132</v>
       </c>
@@ -939,7 +939,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="10">
         <v>46162</v>
       </c>
@@ -989,7 +989,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="10">
         <v>46195</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="10">
         <v>46223</v>
       </c>
@@ -1086,6 +1086,56 @@
         <v>26.7</v>
       </c>
       <c r="P9" s="14">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="10">
+        <v>46254</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46254</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="14">
+        <v>116</v>
+      </c>
+      <c r="F10" s="14">
+        <v>126</v>
+      </c>
+      <c r="G10" s="14">
+        <v>123</v>
+      </c>
+      <c r="H10" s="14">
+        <v>124</v>
+      </c>
+      <c r="I10" s="14">
+        <v>58</v>
+      </c>
+      <c r="J10" s="14">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="K10" s="14">
+        <v>63.6</v>
+      </c>
+      <c r="L10" s="14">
+        <v>63.6</v>
+      </c>
+      <c r="M10" s="14">
+        <v>26.2</v>
+      </c>
+      <c r="N10" s="14">
+        <v>27.9</v>
+      </c>
+      <c r="O10" s="14">
+        <v>26.7</v>
+      </c>
+      <c r="P10" s="14">
         <v>26.7</v>
       </c>
     </row>
@@ -1105,21 +1155,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
   <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.69921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="11.5" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="25" width="9" style="14"/>
     <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="7" customFormat="1">
       <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
@@ -1170,7 +1220,7 @@
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="19"/>
@@ -1213,7 +1263,7 @@
       <c r="X2" s="8"/>
       <c r="Y2" s="8"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="10">
         <v>46022</v>
       </c>
@@ -1264,7 +1314,7 @@
       <c r="X3" s="8"/>
       <c r="Y3" s="8"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="10">
         <v>46052</v>
       </c>
@@ -1315,7 +1365,7 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="10">
         <v>46079</v>
       </c>
@@ -1353,7 +1403,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="10">
         <v>46111</v>
       </c>
@@ -1391,7 +1441,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="10">
         <v>46141</v>
       </c>
@@ -1429,7 +1479,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="10">
         <v>46171</v>
       </c>
@@ -1467,7 +1517,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="10">
         <v>46203</v>
       </c>
@@ -1505,7 +1555,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="A10" s="10">
         <v>46234</v>
       </c>
@@ -1558,18 +1608,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.8984375" style="13" customWidth="1"/>
+    <col min="5" max="24" width="8.83203125" style="13" customWidth="1"/>
     <col min="25" max="25" width="9" style="14"/>
     <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="7" customFormat="1">
       <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
@@ -1644,7 +1694,7 @@
       </c>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="19"/>
@@ -1711,7 +1761,7 @@
       </c>
       <c r="Y2" s="8"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="15">
         <v>45991</v>
       </c>
@@ -1760,7 +1810,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="8"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="10">
         <v>46022</v>
       </c>
@@ -1835,7 +1885,7 @@
       </c>
       <c r="Y4" s="8"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="10">
         <v>46052</v>
       </c>
@@ -1910,7 +1960,7 @@
       </c>
       <c r="Y5" s="8"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="10">
         <v>46079</v>
       </c>
@@ -1984,7 +2034,7 @@
         <v>161.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="10">
         <v>46119</v>
       </c>
@@ -2058,7 +2108,7 @@
         <v>161.80000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="10">
         <v>46141</v>
       </c>
@@ -2132,7 +2182,7 @@
         <v>169.8</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="10">
         <v>46171</v>
       </c>
@@ -2206,7 +2256,7 @@
         <v>168.7</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="A10" s="10">
         <v>46203</v>
       </c>
@@ -2280,7 +2330,7 @@
         <v>168.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25">
       <c r="A11" s="10">
         <v>46234</v>
       </c>
@@ -2369,25 +2419,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="14"/>
     <col min="26" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="7" customFormat="1">
       <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
@@ -2442,7 +2492,7 @@
       <c r="X1" s="5"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="19"/>
@@ -2489,7 +2539,7 @@
       <c r="X2" s="8"/>
       <c r="Y2" s="8"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="10">
         <v>45962</v>
       </c>
@@ -2544,7 +2594,7 @@
       <c r="X3" s="8"/>
       <c r="Y3" s="8"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="10">
         <v>45992</v>
       </c>
@@ -2599,7 +2649,7 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="10">
         <v>46023</v>
       </c>
@@ -2643,7 +2693,7 @@
         <v>21064</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="10">
         <v>46054</v>
       </c>
@@ -2687,7 +2737,7 @@
         <v>18066</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="10">
         <v>46082</v>
       </c>
@@ -2731,7 +2781,7 @@
         <v>22289</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="10">
         <v>46113</v>
       </c>
@@ -2775,7 +2825,7 @@
         <v>20053</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="10">
         <v>46143</v>
       </c>
@@ -2819,7 +2869,7 @@
         <v>20165</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="A10" s="10">
         <v>46174</v>
       </c>
@@ -2861,6 +2911,50 @@
       </c>
       <c r="N10" s="17">
         <v>20433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46255</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="17">
+        <v>19393</v>
+      </c>
+      <c r="F11" s="17">
+        <v>555</v>
+      </c>
+      <c r="G11" s="17">
+        <v>14249</v>
+      </c>
+      <c r="H11" s="17">
+        <v>931</v>
+      </c>
+      <c r="I11" s="17">
+        <v>11825</v>
+      </c>
+      <c r="J11" s="17">
+        <v>2331</v>
+      </c>
+      <c r="K11" s="17">
+        <v>19185</v>
+      </c>
+      <c r="L11" s="17">
+        <v>15636</v>
+      </c>
+      <c r="M11" s="17">
+        <v>64652</v>
+      </c>
+      <c r="N11" s="17">
+        <v>19451</v>
       </c>
     </row>
   </sheetData>
@@ -2878,20 +2972,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2899,19 +2993,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2919,13 +3013,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2933,31 +3027,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -2965,25 +3059,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>18</v>
